--- a/output/pdf_financials_xlsx/BONE.xlsx
+++ b/output/pdf_financials_xlsx/BONE.xlsx
@@ -4449,16 +4449,16 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.435338</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.435338</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>1.678053</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>1.791967</v>
       </c>
       <c r="F92" s="3" t="n">
         <v>0</v>
@@ -9624,7 +9624,11 @@
           <t>Share-based Payment Reserve – Note 5</t>
         </is>
       </c>
-      <c r="D49" t="inlineStr"/>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E49" t="inlineStr">
         <is>
           <t>-</t>
@@ -9996,7 +10000,11 @@
           <t>Share-based Payment Reserve – Note 6</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr"/>
+      <c r="D54" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E54" s="5" t="n">
         <v>1.435338</v>
       </c>

--- a/output/pdf_financials_xlsx/BONE.xlsx
+++ b/output/pdf_financials_xlsx/BONE.xlsx
@@ -897,7 +897,7 @@
         <v>0</v>
       </c>
       <c r="H12" s="3" t="n">
-        <v>0</v>
+        <v>0.007991</v>
       </c>
       <c r="I12" s="3" t="n">
         <v>0</v>
@@ -1608,7 +1608,7 @@
         <v>-1.033193</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-1.034409</v>
+        <v>-1.0424</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-1.09543</v>
@@ -1694,7 +1694,7 @@
         <v>-1.033193</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.034409</v>
+        <v>-1.0424</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>-1.09543</v>
@@ -1903,40 +1903,40 @@
         </is>
       </c>
       <c r="B34" s="3" t="n">
-        <v>0</v>
+        <v>0.04305</v>
       </c>
       <c r="C34" s="3" t="n">
-        <v>0</v>
+        <v>0.048672</v>
       </c>
       <c r="D34" s="3" t="n">
-        <v>0</v>
+        <v>0.06671199999999999</v>
       </c>
       <c r="E34" s="3" t="n">
-        <v>0</v>
+        <v>0.009983000000000001</v>
       </c>
       <c r="F34" s="3" t="n">
-        <v>0</v>
+        <v>0.002043</v>
       </c>
       <c r="G34" s="3" t="n">
-        <v>0</v>
+        <v>0.042153</v>
       </c>
       <c r="H34" s="3" t="n">
-        <v>0</v>
+        <v>0.011851</v>
       </c>
       <c r="I34" s="3" t="n">
-        <v>0</v>
+        <v>0.120583</v>
       </c>
       <c r="J34" s="3" t="n">
-        <v>0</v>
+        <v>0.031038</v>
       </c>
       <c r="K34" s="3" t="n">
-        <v>0</v>
+        <v>0.148219</v>
       </c>
       <c r="L34" s="3" t="n">
-        <v>0</v>
+        <v>0.171841</v>
       </c>
       <c r="M34" s="3" t="n">
-        <v>0</v>
+        <v>0.096063</v>
       </c>
     </row>
     <row r="35">
@@ -1989,40 +1989,40 @@
         </is>
       </c>
       <c r="B36" s="3" t="n">
-        <v>0</v>
+        <v>0.04305</v>
       </c>
       <c r="C36" s="3" t="n">
-        <v>0</v>
+        <v>0.048672</v>
       </c>
       <c r="D36" s="3" t="n">
-        <v>0</v>
+        <v>0.06671199999999999</v>
       </c>
       <c r="E36" s="3" t="n">
-        <v>0</v>
+        <v>0.009983000000000001</v>
       </c>
       <c r="F36" s="3" t="n">
-        <v>0</v>
+        <v>0.002043</v>
       </c>
       <c r="G36" s="3" t="n">
-        <v>0</v>
+        <v>0.042153</v>
       </c>
       <c r="H36" s="3" t="n">
-        <v>0</v>
+        <v>0.011851</v>
       </c>
       <c r="I36" s="3" t="n">
-        <v>0</v>
+        <v>0.120583</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0</v>
+        <v>0.031038</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0</v>
+        <v>0.148219</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0</v>
+        <v>0.171841</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0</v>
+        <v>0.096063</v>
       </c>
     </row>
     <row r="37">
@@ -2505,40 +2505,40 @@
         </is>
       </c>
       <c r="B48" s="3" t="n">
-        <v>0.335311</v>
+        <v>0.292261</v>
       </c>
       <c r="C48" s="3" t="n">
-        <v>0.215976</v>
+        <v>0.167304</v>
       </c>
       <c r="D48" s="3" t="n">
-        <v>0.094664</v>
+        <v>0.027952</v>
       </c>
       <c r="E48" s="3" t="n">
-        <v>0.082055</v>
+        <v>0.072072</v>
       </c>
       <c r="F48" s="3" t="n">
-        <v>0.054904</v>
+        <v>0.052861</v>
       </c>
       <c r="G48" s="3" t="n">
-        <v>0.187102</v>
+        <v>0.144949</v>
       </c>
       <c r="H48" s="3" t="n">
-        <v>0.126406</v>
+        <v>0.114555</v>
       </c>
       <c r="I48" s="3" t="n">
-        <v>0.227626</v>
+        <v>0.107043</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.073494</v>
+        <v>0.042456</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.225145</v>
+        <v>0.07692599999999999</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.228722</v>
+        <v>0.056881</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.148998</v>
+        <v>0.052935</v>
       </c>
     </row>
     <row r="49">
@@ -5807,22 +5807,22 @@
         <v>0</v>
       </c>
       <c r="H124" s="3" t="n">
-        <v>0</v>
+        <v>-0.011964</v>
       </c>
       <c r="I124" s="3" t="n">
-        <v>0</v>
+        <v>-0.012516</v>
       </c>
       <c r="J124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013183</v>
       </c>
       <c r="K124" s="3" t="n">
-        <v>0</v>
+        <v>-0.013516</v>
       </c>
       <c r="L124" s="3" t="n">
-        <v>0</v>
+        <v>-0.022633</v>
       </c>
       <c r="M124" s="3" t="n">
-        <v>0</v>
+        <v>-0.027229</v>
       </c>
     </row>
     <row r="125">
@@ -5850,22 +5850,22 @@
         <v>0</v>
       </c>
       <c r="H125" s="3" t="n">
-        <v>0</v>
+        <v>-0.011964</v>
       </c>
       <c r="I125" s="3" t="n">
-        <v>0</v>
+        <v>-0.012516</v>
       </c>
       <c r="J125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013183</v>
       </c>
       <c r="K125" s="3" t="n">
-        <v>0</v>
+        <v>-0.013516</v>
       </c>
       <c r="L125" s="3" t="n">
-        <v>0</v>
+        <v>-0.022633</v>
       </c>
       <c r="M125" s="3" t="n">
-        <v>0</v>
+        <v>-0.027229</v>
       </c>
     </row>
     <row r="126">
@@ -6442,7 +6442,7 @@
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E2" s="5" t="n">
@@ -11350,7 +11350,11 @@
           <t>Lease payments</t>
         </is>
       </c>
-      <c r="D74" t="inlineStr"/>
+      <c r="D74" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E74" t="inlineStr">
         <is>
           <t>-</t>
@@ -12286,7 +12290,11 @@
           <t>Lease payment</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr"/>
+      <c r="D88" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E88" t="inlineStr">
         <is>
           <t>-</t>
@@ -18466,7 +18474,7 @@
       </c>
       <c r="D173" t="inlineStr">
         <is>
-          <t>InterestIncome</t>
+          <t>InterestIncomeNonOperating</t>
         </is>
       </c>
       <c r="E173" t="inlineStr">

--- a/output/pdf_financials_xlsx/BONE.xlsx
+++ b/output/pdf_financials_xlsx/BONE.xlsx
@@ -664,40 +664,40 @@
         </is>
       </c>
       <c r="B7" s="3" t="n">
-        <v>0.34862</v>
+        <v>0.778899</v>
       </c>
       <c r="C7" s="3" t="n">
-        <v>0.459115</v>
+        <v>0.909257</v>
       </c>
       <c r="D7" s="3" t="n">
-        <v>0.599505</v>
+        <v>0.91989</v>
       </c>
       <c r="E7" s="3" t="n">
-        <v>0.365636</v>
+        <v>0.680145</v>
       </c>
       <c r="F7" s="3" t="n">
-        <v>0.5355839999999999</v>
+        <v>0.86192</v>
       </c>
       <c r="G7" s="3" t="n">
-        <v>0.485366</v>
+        <v>0.811078</v>
       </c>
       <c r="H7" s="3" t="n">
-        <v>0.518369</v>
+        <v>0.8294859999999999</v>
       </c>
       <c r="I7" s="3" t="n">
-        <v>0.473588</v>
+        <v>0.790085</v>
       </c>
       <c r="J7" s="3" t="n">
-        <v>0.464671</v>
+        <v>0.768336</v>
       </c>
       <c r="K7" s="3" t="n">
-        <v>0.356885</v>
+        <v>0.692156</v>
       </c>
       <c r="L7" s="3" t="n">
-        <v>0.311944</v>
+        <v>0.71604</v>
       </c>
       <c r="M7" s="3" t="n">
-        <v>0.32139</v>
+        <v>0.715799</v>
       </c>
     </row>
     <row r="8">
@@ -750,40 +750,40 @@
         </is>
       </c>
       <c r="B9" s="3" t="n">
-        <v>0.013905</v>
+        <v>0.06621199999999999</v>
       </c>
       <c r="C9" s="3" t="n">
-        <v>0.011351</v>
+        <v>0.061468</v>
       </c>
       <c r="D9" s="3" t="n">
-        <v>0.014055</v>
+        <v>0.049272</v>
       </c>
       <c r="E9" s="3" t="n">
-        <v>0.012957</v>
+        <v>0.049989</v>
       </c>
       <c r="F9" s="3" t="n">
-        <v>0.01299</v>
+        <v>0.040407</v>
       </c>
       <c r="G9" s="3" t="n">
-        <v>0.009239000000000001</v>
+        <v>0.049065</v>
       </c>
       <c r="H9" s="3" t="n">
-        <v>0.009225000000000001</v>
+        <v>0.052176</v>
       </c>
       <c r="I9" s="3" t="n">
-        <v>0.011714</v>
+        <v>0.019533</v>
       </c>
       <c r="J9" s="3" t="n">
-        <v>0.038153</v>
+        <v>0.055377</v>
       </c>
       <c r="K9" s="3" t="n">
-        <v>0.014204</v>
+        <v>0.120846</v>
       </c>
       <c r="L9" s="3" t="n">
-        <v>0.012516</v>
+        <v>0.160959</v>
       </c>
       <c r="M9" s="3" t="n">
-        <v>0.012688</v>
+        <v>0.082387</v>
       </c>
     </row>
     <row r="10">
@@ -793,25 +793,25 @@
         </is>
       </c>
       <c r="B10" s="3" t="n">
-        <v>0.362525</v>
+        <v>0.8451109999999999</v>
       </c>
       <c r="C10" s="3" t="n">
-        <v>0.470466</v>
+        <v>0.9707249999999999</v>
       </c>
       <c r="D10" s="3" t="n">
-        <v>0.61356</v>
+        <v>0.969162</v>
       </c>
       <c r="E10" s="3" t="n">
-        <v>0.378593</v>
+        <v>0.7301339999999999</v>
       </c>
       <c r="F10" s="3" t="n">
-        <v>0.548574</v>
+        <v>0.902327</v>
       </c>
       <c r="G10" s="3" t="n">
-        <v>0.494605</v>
+        <v>0.860143</v>
       </c>
       <c r="H10" s="3" t="n">
-        <v>0.527594</v>
+        <v>0.8816619999999999</v>
       </c>
       <c r="I10" s="3" t="n">
         <v>1.09543</v>
@@ -836,25 +836,25 @@
         </is>
       </c>
       <c r="B11" s="3" t="n">
-        <v>-0.362525</v>
+        <v>-0.8451109999999999</v>
       </c>
       <c r="C11" s="3" t="n">
-        <v>-0.470466</v>
+        <v>-0.9707249999999999</v>
       </c>
       <c r="D11" s="3" t="n">
-        <v>-0.61356</v>
+        <v>-0.969162</v>
       </c>
       <c r="E11" s="3" t="n">
-        <v>-0.378593</v>
+        <v>-0.7301339999999999</v>
       </c>
       <c r="F11" s="3" t="n">
-        <v>-0.548574</v>
+        <v>-0.902327</v>
       </c>
       <c r="G11" s="3" t="n">
-        <v>-0.494605</v>
+        <v>-0.860143</v>
       </c>
       <c r="H11" s="3" t="n">
-        <v>-0.527594</v>
+        <v>-0.8816619999999999</v>
       </c>
       <c r="I11" s="3" t="n">
         <v>-1.09543</v>
@@ -1970,16 +1970,16 @@
         <v>0</v>
       </c>
       <c r="J35" s="3" t="n">
-        <v>0</v>
+        <v>0.040155</v>
       </c>
       <c r="K35" s="3" t="n">
-        <v>0</v>
+        <v>0.004889</v>
       </c>
       <c r="L35" s="3" t="n">
-        <v>0</v>
+        <v>0.008082000000000001</v>
       </c>
       <c r="M35" s="3" t="n">
-        <v>0</v>
+        <v>0.007222</v>
       </c>
     </row>
     <row r="36">
@@ -2013,16 +2013,16 @@
         <v>0.120583</v>
       </c>
       <c r="J36" s="3" t="n">
-        <v>0.031038</v>
+        <v>0.07119300000000001</v>
       </c>
       <c r="K36" s="3" t="n">
-        <v>0.148219</v>
+        <v>0.153108</v>
       </c>
       <c r="L36" s="3" t="n">
-        <v>0.171841</v>
+        <v>0.179923</v>
       </c>
       <c r="M36" s="3" t="n">
-        <v>0.096063</v>
+        <v>0.103285</v>
       </c>
     </row>
     <row r="37">
@@ -2529,16 +2529,16 @@
         <v>0.107043</v>
       </c>
       <c r="J48" s="3" t="n">
-        <v>0.042456</v>
+        <v>0.002301</v>
       </c>
       <c r="K48" s="3" t="n">
-        <v>0.07692599999999999</v>
+        <v>0.072037</v>
       </c>
       <c r="L48" s="3" t="n">
-        <v>0.056881</v>
+        <v>0.048799</v>
       </c>
       <c r="M48" s="3" t="n">
-        <v>0.052935</v>
+        <v>0.045713</v>
       </c>
     </row>
     <row r="49">
@@ -2720,10 +2720,10 @@
         </is>
       </c>
       <c r="B53" s="3" t="n">
-        <v>0</v>
+        <v>0.007376</v>
       </c>
       <c r="C53" s="3" t="n">
-        <v>0</v>
+        <v>0.005162</v>
       </c>
       <c r="D53" s="3" t="n">
         <v>0</v>
@@ -2977,22 +2977,22 @@
         <v>9.402644</v>
       </c>
       <c r="H58" s="3" t="n">
-        <v>9.657138</v>
+        <v>9.670684</v>
       </c>
       <c r="I58" s="3" t="n">
-        <v>9.978301999999999</v>
+        <v>9.981688</v>
       </c>
       <c r="J58" s="3" t="n">
-        <v>9.846693</v>
+        <v>9.862029</v>
       </c>
       <c r="K58" s="3" t="n">
-        <v>10.112791</v>
+        <v>10.116626</v>
       </c>
       <c r="L58" s="3" t="n">
-        <v>10.811953</v>
+        <v>10.842832</v>
       </c>
       <c r="M58" s="3" t="n">
-        <v>11.129511</v>
+        <v>11.137231</v>
       </c>
     </row>
     <row r="59">
@@ -3106,22 +3106,22 @@
         <v>0</v>
       </c>
       <c r="H61" s="3" t="n">
-        <v>0.013546</v>
+        <v>0</v>
       </c>
       <c r="I61" s="3" t="n">
-        <v>0.003386</v>
+        <v>0</v>
       </c>
       <c r="J61" s="3" t="n">
-        <v>0.015336</v>
+        <v>0</v>
       </c>
       <c r="K61" s="3" t="n">
-        <v>0.016835</v>
+        <v>0.013</v>
       </c>
       <c r="L61" s="3" t="n">
-        <v>0.030879</v>
+        <v>0</v>
       </c>
       <c r="M61" s="3" t="n">
-        <v>0.00772</v>
+        <v>0</v>
       </c>
     </row>
     <row r="62">
@@ -3389,40 +3389,40 @@
         </is>
       </c>
       <c r="B68" s="3" t="n">
-        <v>0</v>
+        <v>0.51922</v>
       </c>
       <c r="C68" s="3" t="n">
-        <v>0</v>
+        <v>0.521356</v>
       </c>
       <c r="D68" s="3" t="n">
-        <v>0</v>
+        <v>0.40286</v>
       </c>
       <c r="E68" s="3" t="n">
-        <v>0</v>
+        <v>0.514795</v>
       </c>
       <c r="F68" s="3" t="n">
-        <v>0</v>
+        <v>0.372408</v>
       </c>
       <c r="G68" s="3" t="n">
-        <v>0</v>
+        <v>0.363644</v>
       </c>
       <c r="H68" s="3" t="n">
-        <v>0</v>
+        <v>0.635137</v>
       </c>
       <c r="I68" s="3" t="n">
-        <v>0</v>
+        <v>0.466341</v>
       </c>
       <c r="J68" s="3" t="n">
-        <v>0</v>
+        <v>0.560971</v>
       </c>
       <c r="K68" s="3" t="n">
-        <v>0</v>
+        <v>0.466363</v>
       </c>
       <c r="L68" s="3" t="n">
-        <v>0</v>
+        <v>0.557883</v>
       </c>
       <c r="M68" s="3" t="n">
-        <v>0</v>
+        <v>0.443885</v>
       </c>
     </row>
     <row r="69">
@@ -3450,22 +3450,22 @@
         <v>0</v>
       </c>
       <c r="H69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K69" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L69" s="3" t="n">
-        <v>0</v>
+        <v>0.039953</v>
       </c>
       <c r="M69" s="3" t="n">
-        <v>0</v>
+        <v>0.039718</v>
       </c>
     </row>
     <row r="70">
@@ -3536,22 +3536,22 @@
         <v>0</v>
       </c>
       <c r="H71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="K71" s="3" t="n">
-        <v>0</v>
+        <v>0.04</v>
       </c>
       <c r="L71" s="3" t="n">
-        <v>0</v>
+        <v>0.039953</v>
       </c>
       <c r="M71" s="3" t="n">
-        <v>0</v>
+        <v>0.039718</v>
       </c>
     </row>
     <row r="72">
@@ -3693,37 +3693,37 @@
         <v>0</v>
       </c>
       <c r="C75" s="3" t="n">
-        <v>0.521356</v>
+        <v>0</v>
       </c>
       <c r="D75" s="3" t="n">
-        <v>0.45286</v>
+        <v>0.05</v>
       </c>
       <c r="E75" s="3" t="n">
-        <v>1.029879</v>
+        <v>0.515084</v>
       </c>
       <c r="F75" s="3" t="n">
-        <v>0.388721</v>
+        <v>0.016313</v>
       </c>
       <c r="G75" s="3" t="n">
-        <v>0.366823</v>
+        <v>0.003179</v>
       </c>
       <c r="H75" s="3" t="n">
-        <v>0.692381</v>
+        <v>0.017244</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>0.522224</v>
+        <v>0.015883</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.629853</v>
+        <v>0.028882</v>
       </c>
       <c r="K75" s="3" t="n">
-        <v>0.573366</v>
+        <v>0.06700299999999999</v>
       </c>
       <c r="L75" s="3" t="n">
-        <v>0.649376</v>
+        <v>0.05154</v>
       </c>
       <c r="M75" s="3" t="n">
-        <v>0.526112</v>
+        <v>0.042509</v>
       </c>
     </row>
     <row r="76">
@@ -3936,35 +3936,23 @@
           <t>-</t>
         </is>
       </c>
-      <c r="H80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="I80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="J80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="K80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="L80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
-      </c>
-      <c r="M80" s="1" t="inlineStr">
-        <is>
-          <t>-</t>
-        </is>
+      <c r="H80" s="3" t="n">
+        <v>0.004414678231210605</v>
+      </c>
+      <c r="I80" s="3" t="n">
+        <v>0.004146328063695892</v>
+      </c>
+      <c r="J80" s="3" t="n">
+        <v>0.004319036889325976</v>
+      </c>
+      <c r="K80" s="3" t="n">
+        <v>0.004089392065863748</v>
+      </c>
+      <c r="L80" s="3" t="n">
+        <v>0.003851459911819277</v>
+      </c>
+      <c r="M80" s="3" t="n">
+        <v>0.003704899416523583</v>
       </c>
     </row>
     <row r="81">
@@ -4277,40 +4265,40 @@
         </is>
       </c>
       <c r="B88" s="3" t="n">
-        <v>0</v>
+        <v>23.752031</v>
       </c>
       <c r="C88" s="3" t="n">
-        <v>0</v>
+        <v>24.809338</v>
       </c>
       <c r="D88" s="3" t="n">
-        <v>0</v>
+        <v>27.353517</v>
       </c>
       <c r="E88" s="3" t="n">
-        <v>0</v>
+        <v>28.257795</v>
       </c>
       <c r="F88" s="3" t="n">
-        <v>0</v>
+        <v>30.400719</v>
       </c>
       <c r="G88" s="3" t="n">
-        <v>0</v>
+        <v>32.174834</v>
       </c>
       <c r="H88" s="3" t="n">
-        <v>0</v>
+        <v>33.331083</v>
       </c>
       <c r="I88" s="3" t="n">
-        <v>0</v>
+        <v>34.808528</v>
       </c>
       <c r="J88" s="3" t="n">
-        <v>0</v>
+        <v>35.478066</v>
       </c>
       <c r="K88" s="3" t="n">
-        <v>0</v>
+        <v>36.810105</v>
       </c>
       <c r="L88" s="3" t="n">
-        <v>0</v>
+        <v>38.247111</v>
       </c>
       <c r="M88" s="3" t="n">
-        <v>0</v>
+        <v>39.425933</v>
       </c>
     </row>
     <row r="89">
@@ -4461,28 +4449,28 @@
         <v>1.791967</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>1.985259</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>2.021255</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>2.039692</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>2.268014</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>2.268014</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>2.357441</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>2.491993</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>2.584571</v>
       </c>
     </row>
     <row r="93">
@@ -6560,7 +6548,11 @@
           <t>Prepaids – Note 10</t>
         </is>
       </c>
-      <c r="D4" t="inlineStr"/>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>PrepaidAssets</t>
+        </is>
+      </c>
       <c r="E4" t="inlineStr">
         <is>
           <t>-</t>
@@ -6632,7 +6624,11 @@
           <t>Marketable securities – Note 5</t>
         </is>
       </c>
-      <c r="D5" t="inlineStr"/>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>ShortTermInvestments</t>
+        </is>
+      </c>
       <c r="E5" t="inlineStr">
         <is>
           <t>-</t>
@@ -6760,7 +6756,11 @@
           <t>Right-of-use Asset – Note 11</t>
         </is>
       </c>
-      <c r="D7" t="inlineStr"/>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E7" t="inlineStr">
         <is>
           <t>-</t>
@@ -6948,7 +6948,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 10 $</t>
         </is>
       </c>
-      <c r="D10" t="inlineStr"/>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E10" t="inlineStr">
         <is>
           <t>-</t>
@@ -7208,7 +7212,11 @@
           <t>Loan payable – Note 9</t>
         </is>
       </c>
-      <c r="D14" t="inlineStr"/>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E14" t="inlineStr">
         <is>
           <t>-</t>
@@ -7340,7 +7348,11 @@
           <t>Share Capital – Note 6</t>
         </is>
       </c>
-      <c r="D16" t="inlineStr"/>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E16" s="5" t="n">
         <v>23.752031</v>
       </c>
@@ -7398,7 +7410,11 @@
           <t>Reserves – Note 6</t>
         </is>
       </c>
-      <c r="D17" t="inlineStr"/>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E17" t="inlineStr">
         <is>
           <t>-</t>
@@ -8050,7 +8066,11 @@
           <t>Right-of-use Asset – Note 10</t>
         </is>
       </c>
-      <c r="D27" t="inlineStr"/>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E27" t="inlineStr">
         <is>
           <t>-</t>
@@ -8124,7 +8144,11 @@
           <t>Accounts payable and accrued liabilities – Notes 6 and 9 $</t>
         </is>
       </c>
-      <c r="D28" t="inlineStr"/>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E28" t="inlineStr">
         <is>
           <t>-</t>
@@ -8412,7 +8436,11 @@
           <t>Loan Payable – Note 8</t>
         </is>
       </c>
-      <c r="D32" t="inlineStr"/>
+      <c r="D32" t="inlineStr">
+        <is>
+          <t>CurrentDebt</t>
+        </is>
+      </c>
       <c r="E32" t="inlineStr">
         <is>
           <t>-</t>
@@ -8550,7 +8578,11 @@
           <t>Share Capital – Note 5 $</t>
         </is>
       </c>
-      <c r="D34" t="inlineStr"/>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>CapitalStock</t>
+        </is>
+      </c>
       <c r="E34" t="inlineStr">
         <is>
           <t>-</t>
@@ -8612,7 +8644,11 @@
           <t>Reserves – Note 5</t>
         </is>
       </c>
-      <c r="D35" t="inlineStr"/>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E35" t="inlineStr">
         <is>
           <t>-</t>
@@ -8752,7 +8788,11 @@
           <t>Right-of-use Asset – Note 3</t>
         </is>
       </c>
-      <c r="D37" t="inlineStr"/>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>NetPPE</t>
+        </is>
+      </c>
       <c r="E37" t="inlineStr">
         <is>
           <t>-</t>
@@ -9128,7 +9168,11 @@
           <t>Accounts payable and accrued liabilities – Notes 6 and 8 $</t>
         </is>
       </c>
-      <c r="D42" t="inlineStr"/>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E42" t="inlineStr">
         <is>
           <t>-</t>
@@ -9702,7 +9746,11 @@
           <t>Equipment – Note 4</t>
         </is>
       </c>
-      <c r="D50" t="inlineStr"/>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>MachineryFurnitureEquipment</t>
+        </is>
+      </c>
       <c r="E50" s="5" t="n">
         <v>0.007376</v>
       </c>
@@ -9854,7 +9902,11 @@
           <t>Accounts payable and accrued liabilities – Notes 7 and 9 $</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr"/>
+      <c r="D52" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E52" t="inlineStr">
         <is>
           <t>-</t>
@@ -10154,7 +10206,11 @@
           <t>Accounts payable and accrued liabilities – Note 7 and 9 $</t>
         </is>
       </c>
-      <c r="D56" t="inlineStr"/>
+      <c r="D56" t="inlineStr">
+        <is>
+          <t>PayablesAndAccruedExpenses</t>
+        </is>
+      </c>
       <c r="E56" s="5" t="n">
         <v>0.51922</v>
       </c>
@@ -16000,7 +16056,11 @@
           <t>Interest and bank charges – Note 11</t>
         </is>
       </c>
-      <c r="D138" t="inlineStr"/>
+      <c r="D138" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E138" t="inlineStr">
         <is>
           <t>-</t>
@@ -16198,7 +16258,11 @@
           <t>Management fees – Note 10</t>
         </is>
       </c>
-      <c r="D141" t="inlineStr"/>
+      <c r="D141" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E141" t="inlineStr">
         <is>
           <t>-</t>
@@ -16526,7 +16590,11 @@
           <t>Travel and promotion – Note 10</t>
         </is>
       </c>
-      <c r="D146" t="inlineStr"/>
+      <c r="D146" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E146" t="inlineStr">
         <is>
           <t>-</t>
@@ -17328,7 +17396,11 @@
           <t>Rent – Note 10</t>
         </is>
       </c>
-      <c r="D157" t="inlineStr"/>
+      <c r="D157" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E157" t="inlineStr">
         <is>
           <t>-</t>
@@ -17998,7 +18070,11 @@
           <t>Management fees – Note 9</t>
         </is>
       </c>
-      <c r="D166" t="inlineStr"/>
+      <c r="D166" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E166" s="5" t="n">
         <v>0.261216</v>
       </c>
@@ -18134,7 +18210,11 @@
           <t>Rent – Note 9</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E168" s="5" t="n">
         <v>0.026502</v>
       </c>
@@ -18276,7 +18356,11 @@
           <t>Travel and promotion – Note 9</t>
         </is>
       </c>
-      <c r="D170" t="inlineStr"/>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E170" s="5" t="n">
         <v>0.052307</v>
       </c>
@@ -19286,7 +19370,11 @@
           <t>Management fees – Note 8</t>
         </is>
       </c>
-      <c r="D184" t="inlineStr"/>
+      <c r="D184" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E184" t="inlineStr">
         <is>
           <t>-</t>
@@ -19430,7 +19518,11 @@
           <t>Rent – Note 8</t>
         </is>
       </c>
-      <c r="D186" t="inlineStr"/>
+      <c r="D186" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E186" t="inlineStr">
         <is>
           <t>-</t>
@@ -19570,7 +19662,11 @@
           <t>Travel and promotion – Note 8</t>
         </is>
       </c>
-      <c r="D188" t="inlineStr"/>
+      <c r="D188" t="inlineStr">
+        <is>
+          <t>OtherOperatingExpenses</t>
+        </is>
+      </c>
       <c r="E188" t="inlineStr">
         <is>
           <t>-</t>
@@ -20614,7 +20710,11 @@
           <t>Consulting fees – Note 9</t>
         </is>
       </c>
-      <c r="D202" t="inlineStr"/>
+      <c r="D202" t="inlineStr">
+        <is>
+          <t>SellingGeneralAndAdministration</t>
+        </is>
+      </c>
       <c r="E202" s="5" t="n">
         <v>0.142561</v>
       </c>
@@ -20686,7 +20786,11 @@
           <t>Depreciation – Note 4</t>
         </is>
       </c>
-      <c r="D203" t="inlineStr"/>
+      <c r="D203" t="inlineStr">
+        <is>
+          <t>Depreciation</t>
+        </is>
+      </c>
       <c r="E203" s="5" t="n">
         <v>0.00316</v>
       </c>

--- a/output/pdf_financials_xlsx/BONE.xlsx
+++ b/output/pdf_financials_xlsx/BONE.xlsx
@@ -1651,22 +1651,22 @@
         <v>0</v>
       </c>
       <c r="H28" s="3" t="n">
-        <v>0</v>
+        <v>0.010159</v>
       </c>
       <c r="I28" s="3" t="n">
-        <v>0</v>
+        <v>0.01016</v>
       </c>
       <c r="J28" s="3" t="n">
-        <v>0</v>
+        <v>0.011054</v>
       </c>
       <c r="K28" s="3" t="n">
-        <v>0</v>
+        <v>0.011501</v>
       </c>
       <c r="L28" s="3" t="n">
-        <v>0</v>
+        <v>0.019275</v>
       </c>
       <c r="M28" s="3" t="n">
-        <v>0</v>
+        <v>0.023159</v>
       </c>
     </row>
     <row r="29">
@@ -1694,22 +1694,22 @@
         <v>-1.033193</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.0424</v>
+        <v>-1.032241</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>-1.09543</v>
+        <v>-1.08527</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>-1.079234</v>
+        <v>-1.06818</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>-0.903885</v>
+        <v>-0.892384</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>-0.970624</v>
+        <v>-0.951349</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>-0.92334</v>
+        <v>-0.900181</v>
       </c>
     </row>
     <row r="30">
@@ -4763,22 +4763,22 @@
         <v>0</v>
       </c>
       <c r="H100" s="3" t="n">
-        <v>0</v>
+        <v>0.010159</v>
       </c>
       <c r="I100" s="3" t="n">
-        <v>0</v>
+        <v>0.01016</v>
       </c>
       <c r="J100" s="3" t="n">
-        <v>0</v>
+        <v>0.011054</v>
       </c>
       <c r="K100" s="3" t="n">
-        <v>0</v>
+        <v>0.011501</v>
       </c>
       <c r="L100" s="3" t="n">
-        <v>0</v>
+        <v>0.019275</v>
       </c>
       <c r="M100" s="3" t="n">
-        <v>0</v>
+        <v>0.023159</v>
       </c>
     </row>
     <row r="101">
@@ -10490,7 +10490,11 @@
           <t>Depreciation of right-of-use asset</t>
         </is>
       </c>
-      <c r="D60" t="inlineStr"/>
+      <c r="D60" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E60" t="inlineStr">
         <is>
           <t>-</t>
@@ -15868,7 +15872,11 @@
           <t>Depreciation of right-of-use asset – Note 11</t>
         </is>
       </c>
-      <c r="D135" t="inlineStr"/>
+      <c r="D135" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E135" t="inlineStr">
         <is>
           <t>-</t>
@@ -17930,7 +17938,11 @@
           <t>Depreciation of right-of-use asset – Note 10</t>
         </is>
       </c>
-      <c r="D164" t="inlineStr"/>
+      <c r="D164" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E164" t="inlineStr">
         <is>
           <t>-</t>
@@ -18852,7 +18864,11 @@
           <t>Depreciation of right-of-use asset – Note 3</t>
         </is>
       </c>
-      <c r="D177" t="inlineStr"/>
+      <c r="D177" t="inlineStr">
+        <is>
+          <t>DepreciationAmortizationDepletion</t>
+        </is>
+      </c>
       <c r="E177" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/BONE.xlsx
+++ b/output/pdf_financials_xlsx/BONE.xlsx
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="D110" s="3" t="n">
-        <v>0</v>
+        <v>0.066764</v>
       </c>
       <c r="E110" s="3" t="n">
         <v>0</v>
@@ -14512,7 +14512,11 @@
           <t>Accretion expense</t>
         </is>
       </c>
-      <c r="D117" t="inlineStr"/>
+      <c r="D117" t="inlineStr">
+        <is>
+          <t>OtherNonCashItems</t>
+        </is>
+      </c>
       <c r="E117" t="inlineStr">
         <is>
           <t>-</t>
